--- a/data/cox_xlsx/ALKb.CO.xlsx
+++ b/data/cox_xlsx/ALKb.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="438">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -843,7 +843,13 @@
     <t>Total current liabilities</t>
   </si>
   <si>
+    <t>Mortgage debt LT</t>
+  </si>
+  <si>
     <t>Deferred income</t>
+  </si>
+  <si>
+    <t>Bank loans LT</t>
   </si>
   <si>
     <t>Other Loans</t>
@@ -1475,7 +1481,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1557,6 +1563,9 @@
     </xf>
     <xf borderId="5" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -15299,8 +15308,8 @@
       </c>
     </row>
     <row r="101" ht="15.0" customHeight="1">
-      <c r="A101" s="16" t="s">
-        <v>259</v>
+      <c r="A101" s="28" t="s">
+        <v>274</v>
       </c>
       <c r="B101" s="17">
         <v>238.87</v>
@@ -15371,7 +15380,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B102" s="17">
         <v>438.19</v>
@@ -15423,8 +15432,8 @@
       <c r="W102" s="20"/>
     </row>
     <row r="103" ht="15.0" customHeight="1">
-      <c r="A103" s="16" t="s">
-        <v>260</v>
+      <c r="A103" s="28" t="s">
+        <v>276</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -15467,7 +15476,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="16" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -15506,7 +15515,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B105" s="17">
         <v>385.98</v>
@@ -15716,7 +15725,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B109" s="17">
         <v>376.49</v>
@@ -15777,7 +15786,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -15808,7 +15817,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B111" s="17">
         <v>265.76</v>
@@ -15857,7 +15866,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
@@ -15886,7 +15895,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
@@ -15915,7 +15924,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B114" s="19">
         <v>2029.57</v>
@@ -15986,7 +15995,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
@@ -16015,7 +16024,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="18" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B116" s="19">
         <v>4131.91</v>
@@ -16086,7 +16095,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="16" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B117" s="17">
         <v>175.59</v>
@@ -16157,7 +16166,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="16" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B118" s="23">
         <v>-162.94</v>
@@ -16291,7 +16300,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="16" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B120" s="17">
         <v>561.57</v>
@@ -16320,7 +16329,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="16" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
@@ -16351,7 +16360,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="18" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B122" s="27">
         <v>10195.32</v>
@@ -16422,7 +16431,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="16" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -16451,7 +16460,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B124" s="27">
         <v>10195.32</v>
@@ -16522,7 +16531,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="16" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -16551,7 +16560,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B126" s="27">
         <v>14327.23</v>
@@ -16622,7 +16631,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="16" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B127" s="17">
         <v>221.56</v>
@@ -16693,7 +16702,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="16" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B128" s="21">
         <v>1.26</v>
@@ -16764,7 +16773,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="16" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B129" s="17">
         <v>222.82</v>
@@ -16835,7 +16844,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="16" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -16864,7 +16873,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="16" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="17">
@@ -16927,7 +16936,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -16956,7 +16965,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="16" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B133" s="21">
         <v>26.89</v>
@@ -17023,7 +17032,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B134" s="17">
         <v>112.31</v>
@@ -17090,7 +17099,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="16" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B135" s="17">
         <v>126.55</v>
@@ -17157,7 +17166,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="17">
@@ -17218,7 +17227,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="16" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -17255,7 +17264,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B138" s="21">
         <v>72.77</v>
@@ -17318,7 +17327,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="16" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B139" s="17">
         <v>322.71</v>
@@ -17381,7 +17390,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="16" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B140" s="21">
         <v>47.46</v>
@@ -17444,7 +17453,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="16" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B141" s="17">
         <v>201.31</v>
@@ -17515,7 +17524,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="16" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B142" s="21">
         <v>1.26</v>
@@ -17586,7 +17595,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B143" s="17">
         <v>202.57</v>
@@ -17657,7 +17666,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="16" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B144" s="21">
         <v>0.91</v>
@@ -17728,7 +17737,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="16" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B145" s="21">
         <v>18.42</v>
@@ -17799,7 +17808,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B146" s="21">
         <v>18.42</v>
@@ -17870,7 +17879,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="16" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B147" s="21">
         <v>0.08</v>
@@ -17941,7 +17950,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B148" s="21">
         <v>1.84</v>
@@ -17986,7 +17995,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="16" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B149" s="21">
         <v>1.84</v>
@@ -18031,7 +18040,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="16" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B150" s="21">
         <v>0.01</v>
@@ -18076,7 +18085,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="16" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B151" s="17">
         <v>1012.84</v>
@@ -18105,7 +18114,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="16" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B152" s="21">
         <v>6.31</v>
@@ -18134,7 +18143,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="16" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B153" s="17">
         <v>1006.53</v>
@@ -19032,7 +19041,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19416,70 +19425,70 @@
         <v>43</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="T15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="V15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="W15" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -19555,7 +19564,7 @@
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19724,7 +19733,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -19775,7 +19784,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B22" s="17">
         <v>1301.7</v>
@@ -19822,7 +19831,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B23" s="17">
         <v>686.92</v>
@@ -19893,7 +19902,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B24" s="21">
         <v>29.8</v>
@@ -19964,7 +19973,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="16" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B25" s="21">
         <v>70.57</v>
@@ -20035,7 +20044,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B26" s="17">
         <v>514.41</v>
@@ -20106,7 +20115,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -20141,7 +20150,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B28" s="20">
         <v>0.0</v>
@@ -20180,7 +20189,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -20219,7 +20228,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B30" s="23">
         <v>-233.68</v>
@@ -20274,7 +20283,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B31" s="23">
         <v>-197.61</v>
@@ -20343,7 +20352,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B32" s="23">
         <v>-610.08</v>
@@ -20412,7 +20421,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B33" s="17">
         <v>574.0</v>
@@ -20481,7 +20490,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -20538,7 +20547,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B35" s="23">
         <v>-127.03</v>
@@ -20609,7 +20618,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
@@ -20648,7 +20657,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -20679,7 +20688,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="16" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -20708,7 +20717,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="16" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B39" s="17">
         <v>111.35</v>
@@ -20749,7 +20758,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B40" s="22">
         <v>-79.98</v>
@@ -20790,7 +20799,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B41" s="19">
         <v>2849.63</v>
@@ -20861,7 +20870,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B42" s="22">
         <v>-15.68</v>
@@ -20922,7 +20931,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="16" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -20953,7 +20962,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="16" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B44" s="23">
         <v>-131.74</v>
@@ -21014,7 +21023,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="16" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B45" s="23">
         <v>-432.86</v>
@@ -21085,7 +21094,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="16" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
@@ -21116,7 +21125,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="16" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B47" s="22">
         <v>-23.52</v>
@@ -21183,7 +21192,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -21220,7 +21229,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="16" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -21261,7 +21270,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="18" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B50" s="25">
         <v>-603.8</v>
@@ -21332,7 +21341,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B51" s="20">
         <v>0.0</v>
@@ -21371,7 +21380,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
@@ -21408,7 +21417,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="16" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B53" s="22">
         <v>-40.78</v>
@@ -21461,7 +21470,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="16" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B54" s="22">
         <v>-72.14</v>
@@ -21502,7 +21511,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
@@ -21559,7 +21568,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B56" s="23">
         <v>-1079.0</v>
@@ -21598,7 +21607,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
@@ -21655,7 +21664,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="16" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -21702,7 +21711,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="16" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B59" s="20">
         <v>0.0</v>
@@ -21780,7 +21789,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="16" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -21813,7 +21822,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="18" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B62" s="25">
         <v>-1191.92</v>
@@ -21884,7 +21893,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B63" s="22">
         <v>-32.93</v>
@@ -21953,7 +21962,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B64" s="17">
         <v>931.74</v>
@@ -22024,7 +22033,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="16" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B65" s="17">
         <v>1961.55</v>
@@ -22095,7 +22104,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B66" s="17">
         <v>1053.91</v>
@@ -22142,7 +22151,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="18" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B67" s="19">
         <v>1020.98</v>
@@ -22213,7 +22222,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="16" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B68" s="17">
         <v>2245.83</v>
@@ -23206,7 +23215,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23381,31 +23390,31 @@
         <v>38</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -23900,7 +23909,7 @@
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24005,3732 +24014,3732 @@
         <v>69</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Y19" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Z19" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AA19" s="15" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AB19" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AC19" s="15" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AD19" s="15" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AE19" s="15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AF19" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="B21" s="32">
         <v>79277.57</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>56888.92</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>34274.02</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>30852.11</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>47706.01</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>36737.39</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>22817.87</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>13424.82</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>10021.87</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>10329.9</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>10475.3</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>7355.96</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>6337.15</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>3383.12</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>2321.37</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>2872.38</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>3796.31</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>5710.6</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>4839.48</v>
       </c>
-      <c r="U21" s="31"/>
-      <c r="V21" s="32">
+      <c r="U21" s="32"/>
+      <c r="V21" s="33">
         <v>6577.7</v>
       </c>
-      <c r="W21" s="33">
+      <c r="W21" s="34">
         <v>-264.65</v>
       </c>
-      <c r="X21" s="32">
+      <c r="X21" s="33">
         <v>5132.53</v>
       </c>
-      <c r="Y21" s="32">
+      <c r="Y21" s="33">
         <v>4388.44</v>
       </c>
-      <c r="Z21" s="32">
+      <c r="Z21" s="33">
         <v>3605.78</v>
       </c>
-      <c r="AA21" s="32">
+      <c r="AA21" s="33">
         <v>4451.84</v>
       </c>
-      <c r="AB21" s="32">
+      <c r="AB21" s="33">
         <v>4395.1</v>
       </c>
-      <c r="AC21" s="32">
+      <c r="AC21" s="33">
         <v>4157.87</v>
       </c>
-      <c r="AD21" s="32">
+      <c r="AD21" s="33">
         <v>2948.3</v>
       </c>
-      <c r="AE21" s="32">
+      <c r="AE21" s="33">
         <v>2648.42</v>
       </c>
-      <c r="AF21" s="32">
+      <c r="AF21" s="33">
         <v>2251.3</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="B22" s="32">
         <v>52617.91</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>44909.14</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>37081.05</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>31260.53</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>25996.1</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>19585.22</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>13599.04</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>10706.21</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>9496.68</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>7765.66</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>6570.4</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>4890.9</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>3910.51</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>3189.02</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>3602.76</v>
       </c>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="32">
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="33">
         <v>3897.84</v>
       </c>
-      <c r="W22" s="32">
+      <c r="W22" s="33">
         <v>3377.17</v>
       </c>
-      <c r="X22" s="32">
+      <c r="X22" s="33">
         <v>4570.96</v>
       </c>
-      <c r="Y22" s="32">
+      <c r="Y22" s="33">
         <v>4329.24</v>
       </c>
-      <c r="Z22" s="32">
+      <c r="Z22" s="33">
         <v>3592.72</v>
       </c>
-      <c r="AA22" s="32">
+      <c r="AA22" s="33">
         <v>3653.91</v>
       </c>
-      <c r="AB22" s="32">
+      <c r="AB22" s="33">
         <v>3194.17</v>
       </c>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="B24" s="32">
         <v>80577.89</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>55945.22</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>33837.36</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>30182.25</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>47011.22</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>35829.25</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>21929.75</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>12965.73</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>9959.7</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>10409.38</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>10427.7</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>7313.47</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>6320.38</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>3525.85</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>3075.86</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>3093.95</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>4193.19</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>6246.83</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>5877.9</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>14327.98</v>
       </c>
-      <c r="V24" s="32">
+      <c r="V24" s="33">
         <v>7647.06</v>
       </c>
-      <c r="W24" s="32">
+      <c r="W24" s="33">
         <v>5452.69</v>
       </c>
-      <c r="X24" s="32">
+      <c r="X24" s="33">
         <v>2493.55</v>
       </c>
-      <c r="Y24" s="32">
+      <c r="Y24" s="33">
         <v>1781.23</v>
       </c>
-      <c r="Z24" s="32">
+      <c r="Z24" s="33">
         <v>1253.05</v>
       </c>
-      <c r="AA24" s="32">
+      <c r="AA24" s="33">
         <v>1517.24</v>
       </c>
-      <c r="AB24" s="32">
+      <c r="AB24" s="33">
         <v>1615.19</v>
       </c>
-      <c r="AC24" s="32">
+      <c r="AC24" s="33">
         <v>2139.08</v>
       </c>
-      <c r="AD24" s="32">
+      <c r="AD24" s="33">
         <v>2395.2</v>
       </c>
-      <c r="AE24" s="32">
+      <c r="AE24" s="33">
         <v>2318.76</v>
       </c>
-      <c r="AF24" s="32">
+      <c r="AF24" s="33">
         <v>2131.67</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>388</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="B25" s="32">
         <v>52283.18</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>44112.2</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>36300.46</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>30511.41</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>25396.11</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>19121.44</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>13325.22</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>10600.06</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>9478.42</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>7795.74</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>6771.85</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>5141.48</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>4228.68</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>3553.05</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>4160.56</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="33">
         <v>6274.52</v>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="33">
         <v>7603.17</v>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="33">
         <v>9265.48</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="33">
         <v>7008.9</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="33">
         <v>6404.69</v>
       </c>
-      <c r="V25" s="32">
+      <c r="V25" s="33">
         <v>3755.25</v>
       </c>
-      <c r="W25" s="32">
+      <c r="W25" s="33">
         <v>2458.58</v>
       </c>
-      <c r="X25" s="32">
+      <c r="X25" s="33">
         <v>1794.4</v>
       </c>
-      <c r="Y25" s="32">
+      <c r="Y25" s="33">
         <v>1705.79</v>
       </c>
-      <c r="Z25" s="32">
+      <c r="Z25" s="33">
         <v>1617.67</v>
       </c>
-      <c r="AA25" s="32">
+      <c r="AA25" s="33">
         <v>1950.14</v>
       </c>
-      <c r="AB25" s="32">
+      <c r="AB25" s="33">
         <v>2055.7</v>
       </c>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="31"/>
-      <c r="AF25" s="31"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>389</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>390</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="B27" s="33">
         <v>361.62</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>251.07</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>151.86</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>135.45</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>230.92</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>176.0</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>107.72</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="35">
         <v>63.69</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="35">
         <v>48.94</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="35">
         <v>56.24</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="35">
         <v>56.34</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="35">
         <v>39.52</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>34.32</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="35">
         <v>19.15</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <v>16.7</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <v>16.8</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="35">
         <v>22.77</v>
       </c>
-      <c r="S27" s="34">
+      <c r="S27" s="35">
         <v>33.92</v>
       </c>
-      <c r="T27" s="34">
+      <c r="T27" s="35">
         <v>31.92</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="35">
         <v>77.81</v>
       </c>
-      <c r="V27" s="34">
+      <c r="V27" s="35">
         <v>41.53</v>
       </c>
-      <c r="W27" s="34">
+      <c r="W27" s="35">
         <v>29.61</v>
       </c>
-      <c r="X27" s="34">
+      <c r="X27" s="35">
         <v>13.54</v>
       </c>
-      <c r="Y27" s="34">
+      <c r="Y27" s="35">
         <v>9.67</v>
       </c>
-      <c r="Z27" s="34">
+      <c r="Z27" s="35">
         <v>6.8</v>
       </c>
-      <c r="AA27" s="34">
+      <c r="AA27" s="35">
         <v>8.24</v>
       </c>
-      <c r="AB27" s="34">
+      <c r="AB27" s="35">
         <v>8.77</v>
       </c>
-      <c r="AC27" s="34">
+      <c r="AC27" s="35">
         <v>11.62</v>
       </c>
-      <c r="AD27" s="34">
+      <c r="AD27" s="35">
         <v>13.01</v>
       </c>
-      <c r="AE27" s="34">
+      <c r="AE27" s="35">
         <v>12.59</v>
       </c>
-      <c r="AF27" s="34">
+      <c r="AF27" s="35">
         <v>11.58</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="B28" s="33">
         <v>239.32</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>206.05</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>172.71</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>147.31</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>124.75</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="35">
         <v>95.11</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="35">
         <v>67.61</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="35">
         <v>55.02</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="35">
         <v>50.28</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="35">
         <v>42.18</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="35">
         <v>36.67</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="35">
         <v>27.88</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="35">
         <v>22.96</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="35">
         <v>19.29</v>
       </c>
-      <c r="P28" s="34">
+      <c r="P28" s="35">
         <v>22.59</v>
       </c>
-      <c r="Q28" s="34">
+      <c r="Q28" s="35">
         <v>34.07</v>
       </c>
-      <c r="R28" s="34">
+      <c r="R28" s="35">
         <v>41.29</v>
       </c>
-      <c r="S28" s="34">
+      <c r="S28" s="35">
         <v>50.31</v>
       </c>
-      <c r="T28" s="34">
+      <c r="T28" s="35">
         <v>38.06</v>
       </c>
-      <c r="U28" s="34">
+      <c r="U28" s="35">
         <v>34.78</v>
       </c>
-      <c r="V28" s="34">
+      <c r="V28" s="35">
         <v>20.39</v>
       </c>
-      <c r="W28" s="34">
+      <c r="W28" s="35">
         <v>13.35</v>
       </c>
-      <c r="X28" s="34">
+      <c r="X28" s="35">
         <v>9.74</v>
       </c>
-      <c r="Y28" s="34">
+      <c r="Y28" s="35">
         <v>9.26</v>
       </c>
-      <c r="Z28" s="34">
+      <c r="Z28" s="35">
         <v>8.78</v>
       </c>
-      <c r="AA28" s="34">
+      <c r="AA28" s="35">
         <v>10.59</v>
       </c>
-      <c r="AB28" s="34">
+      <c r="AB28" s="35">
         <v>11.16</v>
       </c>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>393</v>
-      </c>
-      <c r="B30" s="35">
+      <c r="A30" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="B30" s="36">
         <v>2.87</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>-0.26</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>1.29</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>0.3</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>0.54</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>0.29</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>-0.2</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>-2.62</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <v>-8.91</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="36">
         <v>1.97</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>-0.19</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="36">
         <v>1.83</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>-1.78</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="36">
         <v>0.08</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="36">
         <v>8.75</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="36">
         <v>3.51</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>1.06</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="37">
         <v>-3.69</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="36">
         <v>3.16</v>
       </c>
-      <c r="U30" s="35"/>
-      <c r="V30" s="36">
+      <c r="U30" s="36"/>
+      <c r="V30" s="37">
         <v>-0.58</v>
       </c>
-      <c r="W30" s="35">
+      <c r="W30" s="36">
         <v>1.57</v>
       </c>
-      <c r="X30" s="36">
+      <c r="X30" s="37">
         <v>-1.72</v>
       </c>
-      <c r="Y30" s="36">
+      <c r="Y30" s="37">
         <v>-1.42</v>
       </c>
-      <c r="Z30" s="35">
+      <c r="Z30" s="36">
         <v>18.61</v>
       </c>
-      <c r="AA30" s="36">
+      <c r="AA30" s="37">
         <v>-8.42</v>
       </c>
-      <c r="AB30" s="36">
+      <c r="AB30" s="37">
         <v>-18.42</v>
       </c>
-      <c r="AC30" s="36">
+      <c r="AC30" s="37">
         <v>-0.78</v>
       </c>
-      <c r="AD30" s="36">
+      <c r="AD30" s="37">
         <v>-9.11</v>
       </c>
-      <c r="AE30" s="36">
+      <c r="AE30" s="37">
         <v>-13.44</v>
       </c>
-      <c r="AF30" s="36">
+      <c r="AF30" s="37">
         <v>-25.47</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>394</v>
-      </c>
-      <c r="B31" s="35">
+      <c r="A31" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="B31" s="36">
         <v>1.15</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <v>0.38</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="36">
         <v>0.47</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <v>0.03</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="37">
         <v>-0.74</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="37">
         <v>-1.02</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <v>-1.51</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>-1.51</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>-1.27</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <v>0.52</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="36">
         <v>0.97</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="36">
         <v>1.77</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <v>1.61</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="36">
         <v>1.27</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="36">
         <v>2.0</v>
       </c>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35">
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="36"/>
+      <c r="U31" s="36"/>
+      <c r="V31" s="36">
         <v>1.24</v>
       </c>
-      <c r="W31" s="35">
+      <c r="W31" s="36">
         <v>1.17</v>
       </c>
-      <c r="X31" s="36">
+      <c r="X31" s="37">
         <v>-2.75</v>
       </c>
-      <c r="Y31" s="36">
+      <c r="Y31" s="37">
         <v>-2.56</v>
       </c>
-      <c r="Z31" s="36">
+      <c r="Z31" s="37">
         <v>-4.44</v>
       </c>
-      <c r="AA31" s="36">
+      <c r="AA31" s="37">
         <v>-9.8</v>
       </c>
-      <c r="AB31" s="36">
+      <c r="AB31" s="37">
         <v>-13.14</v>
       </c>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="35"/>
-      <c r="AE31" s="35"/>
-      <c r="AF31" s="35"/>
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="36"/>
+      <c r="AE31" s="36"/>
+      <c r="AF31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
-      <c r="AF32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>396</v>
-      </c>
-      <c r="B33" s="35">
+      <c r="A33" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="B33" s="36">
         <v>0.0</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>0.0</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>0.0</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>0.0</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>0.0</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>0.0</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>0.0</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>0.0</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>0.68</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>0.54</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>0.57</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="36">
         <v>0.77</v>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="36">
         <v>0.81</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="36">
         <v>1.29</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>1.12</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>1.12</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>0.88</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="36">
         <v>4.57</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="36">
         <v>0.24</v>
       </c>
-      <c r="U33" s="35">
+      <c r="U33" s="36">
         <v>0.26</v>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="36">
         <v>0.47</v>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="36">
         <v>0.26</v>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="36">
         <v>0.6</v>
       </c>
-      <c r="Y33" s="35">
+      <c r="Y33" s="36">
         <v>0.83</v>
       </c>
-      <c r="Z33" s="35">
+      <c r="Z33" s="36">
         <v>1.05</v>
       </c>
-      <c r="AA33" s="35">
+      <c r="AA33" s="36">
         <v>1.72</v>
       </c>
-      <c r="AB33" s="35">
+      <c r="AB33" s="36">
         <v>1.15</v>
       </c>
-      <c r="AC33" s="35">
+      <c r="AC33" s="36">
         <v>0.9</v>
       </c>
-      <c r="AD33" s="35">
+      <c r="AD33" s="36">
         <v>0.67</v>
       </c>
-      <c r="AE33" s="35">
+      <c r="AE33" s="36">
         <v>0.65</v>
       </c>
-      <c r="AF33" s="35">
+      <c r="AF33" s="36">
         <v>0.73</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>397</v>
-      </c>
-      <c r="B34" s="35">
+      <c r="A34" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="B34" s="36">
         <v>0.0</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>0.0</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>0.0</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>0.0</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>0.05</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>0.15</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>0.29</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <v>0.48</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="36">
         <v>0.66</v>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="36">
         <v>0.72</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="36">
         <v>0.83</v>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="36">
         <v>0.97</v>
       </c>
-      <c r="N34" s="35">
+      <c r="N34" s="36">
         <v>1.01</v>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="36">
         <v>2.02</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="36">
         <v>1.66</v>
       </c>
-      <c r="Q34" s="35">
+      <c r="Q34" s="36">
         <v>1.1</v>
       </c>
-      <c r="R34" s="35">
+      <c r="R34" s="36">
         <v>0.97</v>
       </c>
-      <c r="S34" s="35">
+      <c r="S34" s="36">
         <v>0.88</v>
       </c>
-      <c r="T34" s="35">
+      <c r="T34" s="36">
         <v>0.32</v>
       </c>
-      <c r="U34" s="35">
+      <c r="U34" s="36">
         <v>0.37</v>
       </c>
-      <c r="V34" s="35">
+      <c r="V34" s="36">
         <v>0.5</v>
       </c>
-      <c r="W34" s="35">
+      <c r="W34" s="36">
         <v>0.66</v>
       </c>
-      <c r="X34" s="35">
+      <c r="X34" s="36">
         <v>1.02</v>
       </c>
-      <c r="Y34" s="35">
+      <c r="Y34" s="36">
         <v>1.11</v>
       </c>
-      <c r="Z34" s="35">
+      <c r="Z34" s="36">
         <v>1.05</v>
       </c>
-      <c r="AA34" s="35">
+      <c r="AA34" s="36">
         <v>0.96</v>
       </c>
-      <c r="AB34" s="35">
+      <c r="AB34" s="36">
         <v>0.8</v>
       </c>
-      <c r="AC34" s="35"/>
-      <c r="AD34" s="35"/>
-      <c r="AE34" s="35"/>
-      <c r="AF34" s="35"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
+      <c r="AE34" s="36"/>
+      <c r="AF34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>398</v>
-      </c>
-      <c r="B35" s="35">
+      <c r="A35" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="B35" s="36">
         <v>0.0</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>0.0</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>0.0</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>0.0</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>0.0</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>0.0</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>0.0</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>0.0</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>0.68</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>0.54</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>0.57</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>0.77</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>0.81</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>1.29</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>1.56</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>1.56</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>1.22</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="36">
         <v>6.35</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="36">
         <v>0.33</v>
       </c>
-      <c r="U35" s="35">
+      <c r="U35" s="36">
         <v>0.35</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="36">
         <v>0.65</v>
       </c>
-      <c r="W35" s="35">
+      <c r="W35" s="36">
         <v>0.36</v>
       </c>
-      <c r="X35" s="35">
+      <c r="X35" s="36">
         <v>0.83</v>
       </c>
-      <c r="Y35" s="35">
+      <c r="Y35" s="36">
         <v>1.15</v>
       </c>
-      <c r="Z35" s="35">
+      <c r="Z35" s="36">
         <v>1.46</v>
       </c>
-      <c r="AA35" s="35">
+      <c r="AA35" s="36">
         <v>2.3</v>
       </c>
-      <c r="AB35" s="35">
+      <c r="AB35" s="36">
         <v>1.54</v>
       </c>
-      <c r="AC35" s="35">
+      <c r="AC35" s="36">
         <v>1.2</v>
       </c>
-      <c r="AD35" s="35">
+      <c r="AD35" s="36">
         <v>0.89</v>
       </c>
-      <c r="AE35" s="35">
+      <c r="AE35" s="36">
         <v>0.86</v>
       </c>
-      <c r="AF35" s="35">
+      <c r="AF35" s="36">
         <v>0.97</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="B36" s="35">
+      <c r="A36" s="31" t="s">
+        <v>401</v>
+      </c>
+      <c r="B36" s="36">
         <v>0.0</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>0.0</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>0.0</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>0.0</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>0.05</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>0.15</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>0.29</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>0.48</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>0.66</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <v>0.72</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <v>0.88</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="36">
         <v>1.09</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <v>1.22</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="36">
         <v>2.7</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="36">
         <v>2.3</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="36">
         <v>1.53</v>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="36">
         <v>1.35</v>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="36">
         <v>1.22</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="36">
         <v>0.45</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="36">
         <v>0.51</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="36">
         <v>0.69</v>
       </c>
-      <c r="W36" s="35">
+      <c r="W36" s="36">
         <v>0.91</v>
       </c>
-      <c r="X36" s="35">
+      <c r="X36" s="36">
         <v>1.38</v>
       </c>
-      <c r="Y36" s="35">
+      <c r="Y36" s="36">
         <v>1.5</v>
       </c>
-      <c r="Z36" s="35">
+      <c r="Z36" s="36">
         <v>1.41</v>
       </c>
-      <c r="AA36" s="35">
+      <c r="AA36" s="36">
         <v>1.28</v>
       </c>
-      <c r="AB36" s="35">
+      <c r="AB36" s="36">
         <v>1.06</v>
       </c>
-      <c r="AC36" s="35"/>
-      <c r="AD36" s="35"/>
-      <c r="AE36" s="35"/>
-      <c r="AF36" s="35"/>
+      <c r="AC36" s="36"/>
+      <c r="AD36" s="36"/>
+      <c r="AE36" s="36"/>
+      <c r="AF36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="29"/>
-      <c r="AD37" s="29"/>
-      <c r="AE37" s="29"/>
-      <c r="AF37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="B38" s="34">
+      <c r="A38" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="B38" s="35">
         <v>7.86</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="35">
         <v>6.56</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <v>5.03</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="35">
         <v>5.32</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <v>10.83</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <v>8.67</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <v>5.6</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="35">
         <v>3.28</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="35">
         <v>2.44</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="35">
         <v>3.15</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="35">
         <v>3.17</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="35">
         <v>2.67</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="35">
         <v>2.64</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="35">
         <v>1.67</v>
       </c>
-      <c r="P38" s="34">
+      <c r="P38" s="35">
         <v>1.46</v>
       </c>
-      <c r="Q38" s="34">
+      <c r="Q38" s="35">
         <v>1.58</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R38" s="35">
         <v>2.11</v>
       </c>
-      <c r="S38" s="34">
+      <c r="S38" s="35">
         <v>2.78</v>
       </c>
-      <c r="T38" s="34">
+      <c r="T38" s="35">
         <v>2.84</v>
       </c>
-      <c r="U38" s="31"/>
-      <c r="V38" s="34">
+      <c r="U38" s="32"/>
+      <c r="V38" s="35">
         <v>3.67</v>
       </c>
-      <c r="W38" s="34">
+      <c r="W38" s="35">
         <v>0.91</v>
       </c>
-      <c r="X38" s="34">
+      <c r="X38" s="35">
         <v>1.25</v>
       </c>
-      <c r="Y38" s="34">
+      <c r="Y38" s="35">
         <v>0.9</v>
       </c>
-      <c r="Z38" s="34">
+      <c r="Z38" s="35">
         <v>0.69</v>
       </c>
-      <c r="AA38" s="34">
+      <c r="AA38" s="35">
         <v>0.73</v>
       </c>
-      <c r="AB38" s="34">
+      <c r="AB38" s="35">
         <v>0.73</v>
       </c>
-      <c r="AC38" s="34">
+      <c r="AC38" s="35">
         <v>1.07</v>
       </c>
-      <c r="AD38" s="34">
+      <c r="AD38" s="35">
         <v>0.7</v>
       </c>
-      <c r="AE38" s="34">
+      <c r="AE38" s="35">
         <v>0.88</v>
       </c>
-      <c r="AF38" s="34">
+      <c r="AF38" s="35">
         <v>0.87</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="B39" s="34">
+      <c r="A39" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="B39" s="35">
         <v>7.05</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="35">
         <v>7.04</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="35">
         <v>6.93</v>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="35">
         <v>6.74</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="35">
         <v>6.21</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="35">
         <v>4.6</v>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <v>3.53</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="35">
         <v>2.95</v>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="35">
         <v>2.82</v>
       </c>
-      <c r="K39" s="34">
+      <c r="K39" s="35">
         <v>2.7</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="35">
         <v>2.36</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="35">
         <v>2.03</v>
       </c>
-      <c r="N39" s="34">
+      <c r="N39" s="35">
         <v>1.9</v>
       </c>
-      <c r="O39" s="34">
+      <c r="O39" s="35">
         <v>1.89</v>
       </c>
-      <c r="P39" s="34">
+      <c r="P39" s="35">
         <v>2.14</v>
       </c>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="34">
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="35">
         <v>1.34</v>
       </c>
-      <c r="W39" s="34">
+      <c r="W39" s="35">
         <v>0.9</v>
       </c>
-      <c r="X39" s="34">
+      <c r="X39" s="35">
         <v>0.85</v>
       </c>
-      <c r="Y39" s="34">
+      <c r="Y39" s="35">
         <v>0.82</v>
       </c>
-      <c r="Z39" s="34">
+      <c r="Z39" s="35">
         <v>0.77</v>
       </c>
-      <c r="AA39" s="34">
+      <c r="AA39" s="35">
         <v>0.81</v>
       </c>
-      <c r="AB39" s="34">
+      <c r="AB39" s="35">
         <v>0.83</v>
       </c>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
-      <c r="AE39" s="31"/>
-      <c r="AF39" s="31"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="32"/>
+      <c r="AE39" s="32"/>
+      <c r="AF39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>403</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="29"/>
-      <c r="AF40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="B41" s="34">
+      <c r="A41" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="B41" s="35">
         <v>10.82</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="35">
         <v>9.84</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="35">
         <v>5.93</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="35">
         <v>6.34</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="35">
         <v>13.19</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="35">
         <v>10.8</v>
       </c>
-      <c r="H41" s="34">
+      <c r="H41" s="35">
         <v>7.14</v>
       </c>
-      <c r="I41" s="34">
+      <c r="I41" s="35">
         <v>4.26</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="35">
         <v>3.17</v>
       </c>
-      <c r="K41" s="34">
+      <c r="K41" s="35">
         <v>4.28</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="35">
         <v>4.41</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="35">
         <v>3.72</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="35">
         <v>3.77</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="35">
         <v>2.34</v>
       </c>
-      <c r="P41" s="34">
+      <c r="P41" s="35">
         <v>2.05</v>
       </c>
-      <c r="Q41" s="34">
+      <c r="Q41" s="35">
         <v>2.26</v>
       </c>
-      <c r="R41" s="34">
+      <c r="R41" s="35">
         <v>2.8</v>
       </c>
-      <c r="S41" s="34">
+      <c r="S41" s="35">
         <v>3.66</v>
       </c>
-      <c r="T41" s="34">
+      <c r="T41" s="35">
         <v>3.69</v>
       </c>
-      <c r="U41" s="31"/>
-      <c r="V41" s="34">
+      <c r="U41" s="32"/>
+      <c r="V41" s="35">
         <v>4.82</v>
       </c>
-      <c r="W41" s="34">
+      <c r="W41" s="35">
         <v>0.95</v>
       </c>
-      <c r="X41" s="34">
+      <c r="X41" s="35">
         <v>3.36</v>
       </c>
-      <c r="Y41" s="34">
+      <c r="Y41" s="35">
         <v>2.97</v>
       </c>
-      <c r="Z41" s="34">
+      <c r="Z41" s="35">
         <v>2.32</v>
       </c>
-      <c r="AA41" s="34">
+      <c r="AA41" s="35">
         <v>2.57</v>
       </c>
-      <c r="AB41" s="34">
+      <c r="AB41" s="35">
         <v>2.58</v>
       </c>
-      <c r="AC41" s="34">
+      <c r="AC41" s="35">
         <v>2.78</v>
       </c>
-      <c r="AD41" s="34">
+      <c r="AD41" s="35">
         <v>0.8</v>
       </c>
-      <c r="AE41" s="34">
+      <c r="AE41" s="35">
         <v>0.84</v>
       </c>
-      <c r="AF41" s="34">
+      <c r="AF41" s="35">
         <v>0.81</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>405</v>
-      </c>
-      <c r="B42" s="34">
+      <c r="A42" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="B42" s="35">
         <v>9.17</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="35">
         <v>8.95</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="35">
         <v>8.43</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="35">
         <v>8.36</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="35">
         <v>7.85</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="35">
         <v>5.95</v>
       </c>
-      <c r="H42" s="34">
+      <c r="H42" s="35">
         <v>4.66</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="35">
         <v>3.96</v>
       </c>
-      <c r="J42" s="34">
+      <c r="J42" s="35">
         <v>3.86</v>
       </c>
-      <c r="K42" s="34">
+      <c r="K42" s="35">
         <v>3.76</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="35">
         <v>3.32</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="35">
         <v>2.86</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="35">
         <v>2.65</v>
       </c>
-      <c r="O42" s="34">
+      <c r="O42" s="35">
         <v>2.6</v>
       </c>
-      <c r="P42" s="34">
+      <c r="P42" s="35">
         <v>2.9</v>
       </c>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="34">
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="35">
         <v>2.01</v>
       </c>
-      <c r="W42" s="34">
+      <c r="W42" s="35">
         <v>1.51</v>
       </c>
-      <c r="X42" s="34">
+      <c r="X42" s="35">
         <v>2.78</v>
       </c>
-      <c r="Y42" s="34">
+      <c r="Y42" s="35">
         <v>2.65</v>
       </c>
-      <c r="Z42" s="34">
+      <c r="Z42" s="35">
         <v>1.64</v>
       </c>
-      <c r="AA42" s="34">
+      <c r="AA42" s="35">
         <v>1.3</v>
       </c>
-      <c r="AB42" s="34">
+      <c r="AB42" s="35">
         <v>1.09</v>
       </c>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
-      <c r="AE42" s="31"/>
-      <c r="AF42" s="31"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
+      <c r="AE42" s="32"/>
+      <c r="AF42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>406</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="29"/>
-      <c r="AC43" s="29"/>
-      <c r="AD43" s="29"/>
-      <c r="AE43" s="29"/>
-      <c r="AF43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>408</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="30"/>
+      <c r="AF43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>407</v>
-      </c>
-      <c r="B44" s="34">
+      <c r="A44" s="31" t="s">
+        <v>409</v>
+      </c>
+      <c r="B44" s="35">
         <v>8.03</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>6.37</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>4.64</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="35">
         <v>4.71</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <v>9.68</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <v>7.87</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <v>5.44</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="35">
         <v>3.58</v>
       </c>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <v>2.52</v>
       </c>
-      <c r="K44" s="34">
+      <c r="K44" s="35">
         <v>3.04</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="35">
         <v>3.36</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="35">
         <v>2.64</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="35">
         <v>2.67</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="35">
         <v>1.62</v>
       </c>
-      <c r="P44" s="34">
+      <c r="P44" s="35">
         <v>1.35</v>
       </c>
-      <c r="Q44" s="34">
+      <c r="Q44" s="35">
         <v>1.48</v>
       </c>
-      <c r="R44" s="34">
+      <c r="R44" s="35">
         <v>2.1</v>
       </c>
-      <c r="S44" s="34">
+      <c r="S44" s="35">
         <v>2.91</v>
       </c>
-      <c r="T44" s="34">
+      <c r="T44" s="35">
         <v>3.66</v>
       </c>
-      <c r="U44" s="34">
+      <c r="U44" s="35">
         <v>8.39</v>
       </c>
-      <c r="V44" s="34">
+      <c r="V44" s="35">
         <v>5.19</v>
       </c>
-      <c r="W44" s="34">
+      <c r="W44" s="35">
         <v>4.67</v>
       </c>
-      <c r="X44" s="34">
+      <c r="X44" s="35">
         <v>0.54</v>
       </c>
-      <c r="Y44" s="34">
+      <c r="Y44" s="35">
         <v>0.41</v>
       </c>
-      <c r="Z44" s="34">
+      <c r="Z44" s="35">
         <v>0.3</v>
       </c>
-      <c r="AA44" s="34">
+      <c r="AA44" s="35">
         <v>0.33</v>
       </c>
-      <c r="AB44" s="34">
+      <c r="AB44" s="35">
         <v>0.38</v>
       </c>
-      <c r="AC44" s="34">
+      <c r="AC44" s="35">
         <v>0.59</v>
       </c>
-      <c r="AD44" s="34">
+      <c r="AD44" s="35">
         <v>0.37</v>
       </c>
-      <c r="AE44" s="34">
+      <c r="AE44" s="35">
         <v>0.43</v>
       </c>
-      <c r="AF44" s="34">
+      <c r="AF44" s="35">
         <v>0.48</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>408</v>
-      </c>
-      <c r="B45" s="34">
+      <c r="A45" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="B45" s="35">
         <v>6.67</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="35">
         <v>6.48</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="35">
         <v>6.34</v>
       </c>
-      <c r="E45" s="34">
+      <c r="E45" s="35">
         <v>6.34</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <v>6.04</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="35">
         <v>4.56</v>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="35">
         <v>3.6</v>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="35">
         <v>3.02</v>
       </c>
-      <c r="J45" s="34">
+      <c r="J45" s="35">
         <v>2.85</v>
       </c>
-      <c r="K45" s="34">
+      <c r="K45" s="35">
         <v>2.7</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="35">
         <v>2.35</v>
       </c>
-      <c r="M45" s="34">
+      <c r="M45" s="35">
         <v>1.96</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="35">
         <v>1.84</v>
       </c>
-      <c r="O45" s="34">
+      <c r="O45" s="35">
         <v>1.84</v>
       </c>
-      <c r="P45" s="34">
+      <c r="P45" s="35">
         <v>2.19</v>
       </c>
-      <c r="Q45" s="34">
+      <c r="Q45" s="35">
         <v>3.53</v>
       </c>
-      <c r="R45" s="34">
+      <c r="R45" s="35">
         <v>4.35</v>
       </c>
-      <c r="S45" s="34">
+      <c r="S45" s="35">
         <v>4.95</v>
       </c>
-      <c r="T45" s="34">
+      <c r="T45" s="35">
         <v>3.43</v>
       </c>
-      <c r="U45" s="34">
+      <c r="U45" s="35">
         <v>2.41</v>
       </c>
-      <c r="V45" s="34">
+      <c r="V45" s="35">
         <v>1.17</v>
       </c>
-      <c r="W45" s="34">
+      <c r="W45" s="35">
         <v>0.66</v>
       </c>
-      <c r="X45" s="34">
+      <c r="X45" s="35">
         <v>0.39</v>
       </c>
-      <c r="Y45" s="34">
+      <c r="Y45" s="35">
         <v>0.39</v>
       </c>
-      <c r="Z45" s="34">
+      <c r="Z45" s="35">
         <v>0.38</v>
       </c>
-      <c r="AA45" s="34">
+      <c r="AA45" s="35">
         <v>0.41</v>
       </c>
-      <c r="AB45" s="34">
+      <c r="AB45" s="35">
         <v>0.44</v>
       </c>
-      <c r="AC45" s="31"/>
-      <c r="AD45" s="31"/>
-      <c r="AE45" s="31"/>
-      <c r="AF45" s="31"/>
+      <c r="AC45" s="32"/>
+      <c r="AD45" s="32"/>
+      <c r="AE45" s="32"/>
+      <c r="AF45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
-      <c r="AC46" s="29"/>
-      <c r="AD46" s="29"/>
-      <c r="AE46" s="29"/>
-      <c r="AF46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>411</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
+      <c r="AE46" s="30"/>
+      <c r="AF46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>410</v>
-      </c>
-      <c r="B47" s="34">
+      <c r="A47" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="B47" s="35">
         <v>34.8</v>
       </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="34">
+      <c r="C47" s="32"/>
+      <c r="D47" s="35">
         <v>77.75</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="33">
         <v>337.51</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="33">
         <v>184.88</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="33">
         <v>347.92</v>
       </c>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="34">
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="35">
         <v>50.67</v>
       </c>
-      <c r="L47" s="31"/>
-      <c r="M47" s="34">
+      <c r="L47" s="32"/>
+      <c r="M47" s="35">
         <v>54.5</v>
       </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="32">
+      <c r="N47" s="32"/>
+      <c r="O47" s="33">
         <v>1269.18</v>
       </c>
-      <c r="P47" s="34">
+      <c r="P47" s="35">
         <v>11.43</v>
       </c>
-      <c r="Q47" s="34">
+      <c r="Q47" s="35">
         <v>28.45</v>
       </c>
-      <c r="R47" s="34">
+      <c r="R47" s="35">
         <v>94.62</v>
       </c>
-      <c r="S47" s="31"/>
-      <c r="T47" s="34">
+      <c r="S47" s="32"/>
+      <c r="T47" s="35">
         <v>31.61</v>
       </c>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="34">
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="35">
         <v>63.8</v>
       </c>
-      <c r="X47" s="31"/>
-      <c r="Y47" s="31"/>
-      <c r="Z47" s="34">
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
+      <c r="Z47" s="35">
         <v>5.37</v>
       </c>
-      <c r="AA47" s="31"/>
-      <c r="AB47" s="31"/>
-      <c r="AC47" s="31"/>
-      <c r="AD47" s="31"/>
-      <c r="AE47" s="31"/>
-      <c r="AF47" s="31"/>
+      <c r="AA47" s="32"/>
+      <c r="AB47" s="32"/>
+      <c r="AC47" s="32"/>
+      <c r="AD47" s="32"/>
+      <c r="AE47" s="32"/>
+      <c r="AF47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B48" s="34">
+      <c r="A48" s="31" t="s">
+        <v>413</v>
+      </c>
+      <c r="B48" s="35">
         <v>87.19</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <v>264.65</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <v>212.18</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="33">
         <v>3377.64</v>
       </c>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="32">
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="33">
         <v>193.42</v>
       </c>
-      <c r="L48" s="32">
+      <c r="L48" s="33">
         <v>102.67</v>
       </c>
-      <c r="M48" s="34">
+      <c r="M48" s="35">
         <v>56.43</v>
       </c>
-      <c r="N48" s="34">
+      <c r="N48" s="35">
         <v>62.12</v>
       </c>
-      <c r="O48" s="34">
+      <c r="O48" s="35">
         <v>79.03</v>
       </c>
-      <c r="P48" s="34">
+      <c r="P48" s="35">
         <v>49.94</v>
       </c>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="31"/>
-      <c r="T48" s="31"/>
-      <c r="U48" s="31"/>
-      <c r="V48" s="34">
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="35">
         <v>80.94</v>
       </c>
-      <c r="W48" s="34">
+      <c r="W48" s="35">
         <v>85.27</v>
       </c>
-      <c r="X48" s="31"/>
-      <c r="Y48" s="31"/>
-      <c r="Z48" s="31"/>
-      <c r="AA48" s="31"/>
-      <c r="AB48" s="31"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="31"/>
-      <c r="AE48" s="31"/>
-      <c r="AF48" s="31"/>
+      <c r="X48" s="32"/>
+      <c r="Y48" s="32"/>
+      <c r="Z48" s="32"/>
+      <c r="AA48" s="32"/>
+      <c r="AB48" s="32"/>
+      <c r="AC48" s="32"/>
+      <c r="AD48" s="32"/>
+      <c r="AE48" s="32"/>
+      <c r="AF48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
-      <c r="AC49" s="29"/>
-      <c r="AD49" s="29"/>
-      <c r="AE49" s="29"/>
-      <c r="AF49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
+      <c r="AF49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B50" s="34">
+      <c r="A50" s="31" t="s">
+        <v>415</v>
+      </c>
+      <c r="B50" s="35">
         <v>33.47</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="35">
         <v>32.61</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="35">
         <v>30.68</v>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="35">
         <v>34.63</v>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="35">
         <v>79.12</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <v>102.56</v>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="35">
         <v>84.37</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="33">
         <v>453.56</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="33">
         <v>319.21</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>21.06</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="35">
         <v>17.18</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="35">
         <v>20.03</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="35">
         <v>31.92</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="35">
         <v>21.39</v>
       </c>
-      <c r="P50" s="34">
+      <c r="P50" s="35">
         <v>8.17</v>
       </c>
-      <c r="Q50" s="34">
+      <c r="Q50" s="35">
         <v>10.69</v>
       </c>
-      <c r="R50" s="34">
+      <c r="R50" s="35">
         <v>15.35</v>
       </c>
-      <c r="S50" s="34">
+      <c r="S50" s="35">
         <v>21.56</v>
       </c>
-      <c r="T50" s="34">
+      <c r="T50" s="35">
         <v>17.2</v>
       </c>
-      <c r="U50" s="34">
+      <c r="U50" s="35">
         <v>89.17</v>
       </c>
-      <c r="V50" s="34">
+      <c r="V50" s="35">
         <v>46.28</v>
       </c>
-      <c r="W50" s="34">
+      <c r="W50" s="35">
         <v>0.63</v>
       </c>
-      <c r="X50" s="34">
+      <c r="X50" s="35">
         <v>5.83</v>
       </c>
-      <c r="Y50" s="34">
+      <c r="Y50" s="35">
         <v>5.23</v>
       </c>
-      <c r="Z50" s="34">
+      <c r="Z50" s="35">
         <v>3.52</v>
       </c>
-      <c r="AA50" s="34">
+      <c r="AA50" s="35">
         <v>5.32</v>
       </c>
-      <c r="AB50" s="34">
+      <c r="AB50" s="35">
         <v>5.06</v>
       </c>
-      <c r="AC50" s="34">
+      <c r="AC50" s="35">
         <v>7.66</v>
       </c>
-      <c r="AD50" s="34">
+      <c r="AD50" s="35">
         <v>4.73</v>
       </c>
-      <c r="AE50" s="34">
+      <c r="AE50" s="35">
         <v>5.52</v>
       </c>
-      <c r="AF50" s="34">
+      <c r="AF50" s="35">
         <v>5.52</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="B51" s="34">
+      <c r="A51" s="31" t="s">
+        <v>416</v>
+      </c>
+      <c r="B51" s="35">
         <v>37.92</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="35">
         <v>45.53</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="35">
         <v>55.19</v>
       </c>
-      <c r="E51" s="34">
+      <c r="E51" s="35">
         <v>72.19</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <v>101.21</v>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="35">
         <v>73.53</v>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="35">
         <v>43.3</v>
       </c>
-      <c r="I51" s="34">
+      <c r="I51" s="35">
         <v>31.51</v>
       </c>
-      <c r="J51" s="34">
+      <c r="J51" s="35">
         <v>25.56</v>
       </c>
-      <c r="K51" s="34">
+      <c r="K51" s="35">
         <v>20.96</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="35">
         <v>17.79</v>
       </c>
-      <c r="M51" s="34">
+      <c r="M51" s="35">
         <v>16.49</v>
       </c>
-      <c r="N51" s="34">
+      <c r="N51" s="35">
         <v>15.4</v>
       </c>
-      <c r="O51" s="34">
+      <c r="O51" s="35">
         <v>14.17</v>
       </c>
-      <c r="P51" s="34">
+      <c r="P51" s="35">
         <v>14.01</v>
       </c>
-      <c r="Q51" s="34">
+      <c r="Q51" s="35">
         <v>24.79</v>
       </c>
-      <c r="R51" s="34">
+      <c r="R51" s="35">
         <v>31.4</v>
       </c>
-      <c r="S51" s="34">
+      <c r="S51" s="35">
         <v>3.93</v>
       </c>
-      <c r="T51" s="34">
+      <c r="T51" s="35">
         <v>3.58</v>
       </c>
-      <c r="U51" s="34">
+      <c r="U51" s="35">
         <v>3.16</v>
       </c>
-      <c r="V51" s="34">
+      <c r="V51" s="35">
         <v>1.84</v>
       </c>
-      <c r="W51" s="34">
+      <c r="W51" s="35">
         <v>1.23</v>
       </c>
-      <c r="X51" s="34">
+      <c r="X51" s="35">
         <v>4.97</v>
       </c>
-      <c r="Y51" s="34">
+      <c r="Y51" s="35">
         <v>5.21</v>
       </c>
-      <c r="Z51" s="34">
+      <c r="Z51" s="35">
         <v>5.08</v>
       </c>
-      <c r="AA51" s="34">
+      <c r="AA51" s="35">
         <v>5.52</v>
       </c>
-      <c r="AB51" s="34">
+      <c r="AB51" s="35">
         <v>5.55</v>
       </c>
-      <c r="AC51" s="31"/>
-      <c r="AD51" s="31"/>
-      <c r="AE51" s="31"/>
-      <c r="AF51" s="31"/>
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="32"/>
+      <c r="AF51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>415</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
-      <c r="AA52" s="29"/>
-      <c r="AB52" s="29"/>
-      <c r="AC52" s="29"/>
-      <c r="AD52" s="29"/>
-      <c r="AE52" s="29"/>
-      <c r="AF52" s="29"/>
+      <c r="A52" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
+      <c r="AE52" s="30"/>
+      <c r="AF52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="B53" s="34">
+      <c r="A53" s="31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B53" s="35">
         <v>42.36</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="35">
         <v>43.25</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="35">
         <v>46.08</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="35">
         <v>63.47</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="33">
         <v>173.06</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="33">
         <v>1099.38</v>
       </c>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="34">
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="35">
         <v>33.78</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="35">
         <v>25.07</v>
       </c>
-      <c r="M53" s="34">
+      <c r="M53" s="35">
         <v>35.53</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="35">
         <v>98.38</v>
       </c>
-      <c r="O53" s="34">
+      <c r="O53" s="35">
         <v>70.51</v>
       </c>
-      <c r="P53" s="34">
+      <c r="P53" s="35">
         <v>15.89</v>
       </c>
-      <c r="Q53" s="34">
+      <c r="Q53" s="35">
         <v>24.89</v>
       </c>
-      <c r="R53" s="34">
+      <c r="R53" s="35">
         <v>34.48</v>
       </c>
-      <c r="S53" s="34">
+      <c r="S53" s="35">
         <v>54.71</v>
       </c>
-      <c r="T53" s="34">
+      <c r="T53" s="35">
         <v>43.13</v>
       </c>
-      <c r="U53" s="31"/>
-      <c r="V53" s="32">
+      <c r="U53" s="32"/>
+      <c r="V53" s="33">
         <v>322.05</v>
       </c>
-      <c r="W53" s="31"/>
-      <c r="X53" s="34">
+      <c r="W53" s="32"/>
+      <c r="X53" s="35">
         <v>32.05</v>
       </c>
-      <c r="Y53" s="32">
+      <c r="Y53" s="33">
         <v>195.71</v>
       </c>
-      <c r="Z53" s="34">
+      <c r="Z53" s="35">
         <v>28.52</v>
       </c>
-      <c r="AA53" s="31"/>
-      <c r="AB53" s="34">
+      <c r="AA53" s="32"/>
+      <c r="AB53" s="35">
         <v>10.18</v>
       </c>
-      <c r="AC53" s="34">
+      <c r="AC53" s="35">
         <v>10.48</v>
       </c>
-      <c r="AD53" s="34">
+      <c r="AD53" s="35">
         <v>5.75</v>
       </c>
-      <c r="AE53" s="34">
+      <c r="AE53" s="35">
         <v>6.29</v>
       </c>
-      <c r="AF53" s="34">
+      <c r="AF53" s="35">
         <v>6.43</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>417</v>
-      </c>
-      <c r="B54" s="34">
+      <c r="A54" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="B54" s="35">
         <v>54.91</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="35">
         <v>76.87</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="33">
         <v>125.53</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="33">
         <v>325.18</v>
       </c>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="32">
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="33">
         <v>197.2</v>
       </c>
-      <c r="I54" s="34">
+      <c r="I54" s="35">
         <v>84.75</v>
       </c>
-      <c r="J54" s="34">
+      <c r="J54" s="35">
         <v>53.67</v>
       </c>
-      <c r="K54" s="34">
+      <c r="K54" s="35">
         <v>37.39</v>
       </c>
-      <c r="L54" s="34">
+      <c r="L54" s="35">
         <v>33.45</v>
       </c>
-      <c r="M54" s="34">
+      <c r="M54" s="35">
         <v>36.34</v>
       </c>
-      <c r="N54" s="34">
+      <c r="N54" s="35">
         <v>36.21</v>
       </c>
-      <c r="O54" s="34">
+      <c r="O54" s="35">
         <v>32.67</v>
       </c>
-      <c r="P54" s="34">
+      <c r="P54" s="35">
         <v>31.75</v>
       </c>
-      <c r="Q54" s="34">
+      <c r="Q54" s="35">
         <v>77.23</v>
       </c>
-      <c r="R54" s="32">
+      <c r="R54" s="33">
         <v>116.93</v>
       </c>
-      <c r="S54" s="32">
+      <c r="S54" s="33">
         <v>450.84</v>
       </c>
-      <c r="T54" s="32">
+      <c r="T54" s="33">
         <v>545.08</v>
       </c>
-      <c r="U54" s="31"/>
-      <c r="V54" s="32">
+      <c r="U54" s="32"/>
+      <c r="V54" s="33">
         <v>435.77</v>
       </c>
-      <c r="W54" s="31"/>
-      <c r="X54" s="34">
+      <c r="W54" s="32"/>
+      <c r="X54" s="35">
         <v>34.41</v>
       </c>
-      <c r="Y54" s="34">
+      <c r="Y54" s="35">
         <v>22.22</v>
       </c>
-      <c r="Z54" s="34">
+      <c r="Z54" s="35">
         <v>11.69</v>
       </c>
-      <c r="AA54" s="34">
+      <c r="AA54" s="35">
         <v>9.09</v>
       </c>
-      <c r="AB54" s="34">
+      <c r="AB54" s="35">
         <v>7.19</v>
       </c>
-      <c r="AC54" s="31"/>
-      <c r="AD54" s="31"/>
-      <c r="AE54" s="31"/>
-      <c r="AF54" s="31"/>
+      <c r="AC54" s="32"/>
+      <c r="AD54" s="32"/>
+      <c r="AE54" s="32"/>
+      <c r="AF54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
-      <c r="AA55" s="29"/>
-      <c r="AB55" s="29"/>
-      <c r="AC55" s="29"/>
-      <c r="AD55" s="29"/>
-      <c r="AE55" s="29"/>
-      <c r="AF55" s="29"/>
+      <c r="A55" s="29" t="s">
+        <v>420</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30"/>
+      <c r="AE55" s="30"/>
+      <c r="AF55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="B56" s="34">
+      <c r="A56" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="B56" s="35">
         <v>42.01</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="35">
         <v>39.34</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="35">
         <v>45.98</v>
       </c>
-      <c r="E56" s="34">
+      <c r="E56" s="35">
         <v>62.54</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="33">
         <v>158.58</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="33">
         <v>436.28</v>
       </c>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="32">
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="33">
         <v>7341.27</v>
       </c>
-      <c r="K56" s="34">
+      <c r="K56" s="35">
         <v>33.78</v>
       </c>
-      <c r="L56" s="34">
+      <c r="L56" s="35">
         <v>24.92</v>
       </c>
-      <c r="M56" s="34">
+      <c r="M56" s="35">
         <v>27.96</v>
       </c>
-      <c r="N56" s="34">
+      <c r="N56" s="35">
         <v>72.31</v>
       </c>
-      <c r="O56" s="34">
+      <c r="O56" s="35">
         <v>32.27</v>
       </c>
-      <c r="P56" s="34">
+      <c r="P56" s="35">
         <v>15.89</v>
       </c>
-      <c r="Q56" s="34">
+      <c r="Q56" s="35">
         <v>24.89</v>
       </c>
-      <c r="R56" s="34">
+      <c r="R56" s="35">
         <v>34.48</v>
       </c>
-      <c r="S56" s="34">
+      <c r="S56" s="35">
         <v>54.71</v>
       </c>
-      <c r="T56" s="34">
+      <c r="T56" s="35">
         <v>28.22</v>
       </c>
-      <c r="U56" s="32">
+      <c r="U56" s="33">
         <v>115.26</v>
       </c>
-      <c r="V56" s="32">
+      <c r="V56" s="33">
         <v>322.05</v>
       </c>
-      <c r="W56" s="34">
+      <c r="W56" s="35">
         <v>0.65</v>
       </c>
-      <c r="X56" s="34">
+      <c r="X56" s="35">
         <v>17.28</v>
       </c>
-      <c r="Y56" s="34">
+      <c r="Y56" s="35">
         <v>15.18</v>
       </c>
-      <c r="Z56" s="34">
+      <c r="Z56" s="35">
         <v>11.69</v>
       </c>
-      <c r="AA56" s="34">
+      <c r="AA56" s="35">
         <v>29.01</v>
       </c>
-      <c r="AB56" s="34">
+      <c r="AB56" s="35">
         <v>16.12</v>
       </c>
-      <c r="AC56" s="34">
+      <c r="AC56" s="35">
         <v>33.04</v>
       </c>
-      <c r="AD56" s="34">
+      <c r="AD56" s="35">
         <v>14.95</v>
       </c>
-      <c r="AE56" s="34">
+      <c r="AE56" s="35">
         <v>12.93</v>
       </c>
-      <c r="AF56" s="34">
+      <c r="AF56" s="35">
         <v>13.36</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="B57" s="34">
+      <c r="A57" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="B57" s="35">
         <v>7.05</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="35">
         <v>7.04</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="35">
         <v>6.93</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="35">
         <v>6.74</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <v>6.21</v>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="35">
         <v>4.6</v>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="35">
         <v>3.53</v>
       </c>
-      <c r="I57" s="34">
+      <c r="I57" s="35">
         <v>2.95</v>
       </c>
-      <c r="J57" s="34">
+      <c r="J57" s="35">
         <v>2.82</v>
       </c>
-      <c r="K57" s="34">
+      <c r="K57" s="35">
         <v>2.7</v>
       </c>
-      <c r="L57" s="34">
+      <c r="L57" s="35">
         <v>2.36</v>
       </c>
-      <c r="M57" s="34">
+      <c r="M57" s="35">
         <v>2.03</v>
       </c>
-      <c r="N57" s="34">
+      <c r="N57" s="35">
         <v>1.9</v>
       </c>
-      <c r="O57" s="34">
+      <c r="O57" s="35">
         <v>1.89</v>
       </c>
-      <c r="P57" s="34">
+      <c r="P57" s="35">
         <v>2.14</v>
       </c>
-      <c r="Q57" s="31"/>
-      <c r="R57" s="31"/>
-      <c r="S57" s="31"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
-      <c r="V57" s="34">
+      <c r="Q57" s="32"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="32"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
+      <c r="V57" s="35">
         <v>1.34</v>
       </c>
-      <c r="W57" s="34">
+      <c r="W57" s="35">
         <v>0.9</v>
       </c>
-      <c r="X57" s="34">
+      <c r="X57" s="35">
         <v>0.85</v>
       </c>
-      <c r="Y57" s="34">
+      <c r="Y57" s="35">
         <v>0.82</v>
       </c>
-      <c r="Z57" s="34">
+      <c r="Z57" s="35">
         <v>0.75</v>
       </c>
-      <c r="AA57" s="34">
+      <c r="AA57" s="35">
         <v>0.78</v>
       </c>
-      <c r="AB57" s="34">
+      <c r="AB57" s="35">
         <v>0.79</v>
       </c>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
-      <c r="AE57" s="31"/>
-      <c r="AF57" s="31"/>
+      <c r="AC57" s="32"/>
+      <c r="AD57" s="32"/>
+      <c r="AE57" s="32"/>
+      <c r="AF57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>421</v>
-      </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
-      <c r="AA58" s="29"/>
-      <c r="AB58" s="29"/>
-      <c r="AC58" s="29"/>
-      <c r="AD58" s="29"/>
-      <c r="AE58" s="29"/>
-      <c r="AF58" s="29"/>
+      <c r="A58" s="29" t="s">
+        <v>423</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
+      <c r="AE58" s="30"/>
+      <c r="AF58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="B59" s="34">
+      <c r="A59" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="B59" s="35">
         <v>0.91</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="35">
         <v>0.64</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="35">
         <v>1.02</v>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="35">
         <v>1.2</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>0.22</v>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="35">
         <v>7.35</v>
       </c>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="37">
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="38">
         <v>-1.53</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="35">
         <v>0.28</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="35">
         <v>0.18</v>
       </c>
-      <c r="N59" s="34">
+      <c r="N59" s="35">
         <v>7.5</v>
       </c>
-      <c r="O59" s="37">
+      <c r="O59" s="38">
         <v>-0.97</v>
       </c>
-      <c r="P59" s="34">
+      <c r="P59" s="35">
         <v>0.28</v>
       </c>
-      <c r="Q59" s="34">
+      <c r="Q59" s="35">
         <v>2.76</v>
       </c>
-      <c r="R59" s="34">
+      <c r="R59" s="35">
         <v>1.4</v>
       </c>
-      <c r="S59" s="37">
+      <c r="S59" s="38">
         <v>-1.73</v>
       </c>
-      <c r="T59" s="34">
+      <c r="T59" s="35">
         <v>0.13</v>
       </c>
-      <c r="U59" s="31"/>
-      <c r="V59" s="34">
+      <c r="U59" s="32"/>
+      <c r="V59" s="35">
         <v>2.66</v>
       </c>
-      <c r="W59" s="31"/>
-      <c r="X59" s="34">
+      <c r="W59" s="32"/>
+      <c r="X59" s="35">
         <v>0.04</v>
       </c>
-      <c r="Y59" s="37">
+      <c r="Y59" s="38">
         <v>-2.4</v>
       </c>
-      <c r="Z59" s="34">
+      <c r="Z59" s="35">
         <v>0.13</v>
       </c>
-      <c r="AA59" s="31"/>
-      <c r="AB59" s="37">
+      <c r="AA59" s="32"/>
+      <c r="AB59" s="38">
         <v>-0.52</v>
       </c>
-      <c r="AC59" s="37">
+      <c r="AC59" s="38">
         <v>-0.21</v>
       </c>
-      <c r="AD59" s="34">
+      <c r="AD59" s="35">
         <v>0.96</v>
       </c>
-      <c r="AE59" s="34">
+      <c r="AE59" s="35">
         <v>0.43</v>
       </c>
-      <c r="AF59" s="31"/>
+      <c r="AF59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="B60" s="34">
+      <c r="A60" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="B60" s="35">
         <v>0.47</v>
       </c>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="31"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="31"/>
-      <c r="K60" s="34">
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="35">
         <v>6.08</v>
       </c>
-      <c r="L60" s="34">
+      <c r="L60" s="35">
         <v>1.52</v>
       </c>
-      <c r="M60" s="34">
+      <c r="M60" s="35">
         <v>3.99</v>
       </c>
-      <c r="N60" s="37">
+      <c r="N60" s="38">
         <v>-4.49</v>
       </c>
-      <c r="O60" s="37">
+      <c r="O60" s="38">
         <v>-1.93</v>
       </c>
-      <c r="P60" s="31"/>
-      <c r="Q60" s="34">
+      <c r="P60" s="32"/>
+      <c r="Q60" s="35">
         <v>1.92</v>
       </c>
-      <c r="R60" s="31"/>
-      <c r="S60" s="34">
+      <c r="R60" s="32"/>
+      <c r="S60" s="35">
         <v>93.67</v>
       </c>
-      <c r="T60" s="34">
+      <c r="T60" s="35">
         <v>7.44</v>
       </c>
-      <c r="U60" s="31"/>
-      <c r="V60" s="31"/>
-      <c r="W60" s="31"/>
-      <c r="X60" s="37">
+      <c r="U60" s="32"/>
+      <c r="V60" s="32"/>
+      <c r="W60" s="32"/>
+      <c r="X60" s="38">
         <v>-1.95</v>
       </c>
-      <c r="Y60" s="37">
+      <c r="Y60" s="38">
         <v>-0.42</v>
       </c>
-      <c r="Z60" s="37">
+      <c r="Z60" s="38">
         <v>-0.35</v>
       </c>
-      <c r="AA60" s="31"/>
-      <c r="AB60" s="31"/>
-      <c r="AC60" s="31"/>
-      <c r="AD60" s="31"/>
-      <c r="AE60" s="31"/>
-      <c r="AF60" s="31"/>
+      <c r="AA60" s="32"/>
+      <c r="AB60" s="32"/>
+      <c r="AC60" s="32"/>
+      <c r="AD60" s="32"/>
+      <c r="AE60" s="32"/>
+      <c r="AF60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>424</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
-      <c r="AA61" s="29"/>
-      <c r="AB61" s="29"/>
-      <c r="AC61" s="29"/>
-      <c r="AD61" s="29"/>
-      <c r="AE61" s="29"/>
-      <c r="AF61" s="29"/>
+      <c r="A61" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
+      <c r="AE61" s="30"/>
+      <c r="AF61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="B62" s="34">
+      <c r="A62" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="B62" s="35">
         <v>7.94</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>6.51</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>4.73</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>4.85</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <v>9.05</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="35">
         <v>7.47</v>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="35">
         <v>5.29</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="35">
         <v>3.47</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="35">
         <v>2.6</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="35">
         <v>2.81</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="35">
         <v>3.17</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="35">
         <v>2.49</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="35">
         <v>2.53</v>
       </c>
-      <c r="O62" s="34">
+      <c r="O62" s="35">
         <v>1.47</v>
       </c>
-      <c r="P62" s="34">
+      <c r="P62" s="35">
         <v>0.95</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="Q62" s="35">
         <v>1.27</v>
       </c>
-      <c r="R62" s="34">
+      <c r="R62" s="35">
         <v>1.76</v>
       </c>
-      <c r="S62" s="34">
+      <c r="S62" s="35">
         <v>2.45</v>
       </c>
-      <c r="T62" s="34">
+      <c r="T62" s="35">
         <v>2.75</v>
       </c>
-      <c r="U62" s="31"/>
-      <c r="V62" s="34">
+      <c r="U62" s="32"/>
+      <c r="V62" s="35">
         <v>4.07</v>
       </c>
-      <c r="W62" s="37">
+      <c r="W62" s="38">
         <v>-0.21</v>
       </c>
-      <c r="X62" s="34">
+      <c r="X62" s="35">
         <v>1.02</v>
       </c>
-      <c r="Y62" s="34">
+      <c r="Y62" s="35">
         <v>0.91</v>
       </c>
-      <c r="Z62" s="34">
+      <c r="Z62" s="35">
         <v>0.78</v>
       </c>
-      <c r="AA62" s="34">
+      <c r="AA62" s="35">
         <v>0.89</v>
       </c>
-      <c r="AB62" s="34">
+      <c r="AB62" s="35">
         <v>0.94</v>
       </c>
-      <c r="AC62" s="34">
+      <c r="AC62" s="35">
         <v>1.05</v>
       </c>
-      <c r="AD62" s="34">
+      <c r="AD62" s="35">
         <v>0.82</v>
       </c>
-      <c r="AE62" s="34">
+      <c r="AE62" s="35">
         <v>0.88</v>
       </c>
-      <c r="AF62" s="34">
+      <c r="AF62" s="35">
         <v>0.91</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="B63" s="34">
+      <c r="A63" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="B63" s="35">
         <v>6.63</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <v>6.39</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="35">
         <v>6.17</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="35">
         <v>6.12</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="35">
         <v>5.85</v>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="35">
         <v>4.46</v>
       </c>
-      <c r="H63" s="34">
+      <c r="H63" s="35">
         <v>3.52</v>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="35">
         <v>2.92</v>
       </c>
-      <c r="J63" s="34">
+      <c r="J63" s="35">
         <v>2.73</v>
       </c>
-      <c r="K63" s="34">
+      <c r="K63" s="35">
         <v>2.52</v>
       </c>
-      <c r="L63" s="34">
+      <c r="L63" s="35">
         <v>2.14</v>
       </c>
-      <c r="M63" s="34">
+      <c r="M63" s="35">
         <v>1.75</v>
       </c>
-      <c r="N63" s="34">
+      <c r="N63" s="35">
         <v>1.59</v>
       </c>
-      <c r="O63" s="34">
+      <c r="O63" s="35">
         <v>1.53</v>
       </c>
-      <c r="P63" s="34">
+      <c r="P63" s="35">
         <v>1.75</v>
       </c>
-      <c r="Q63" s="31"/>
-      <c r="R63" s="31"/>
-      <c r="S63" s="31"/>
-      <c r="T63" s="31"/>
-      <c r="U63" s="31"/>
-      <c r="V63" s="34">
+      <c r="Q63" s="32"/>
+      <c r="R63" s="32"/>
+      <c r="S63" s="32"/>
+      <c r="T63" s="32"/>
+      <c r="U63" s="32"/>
+      <c r="V63" s="35">
         <v>1.11</v>
       </c>
-      <c r="W63" s="34">
+      <c r="W63" s="35">
         <v>0.83</v>
       </c>
-      <c r="X63" s="34">
+      <c r="X63" s="35">
         <v>0.91</v>
       </c>
-      <c r="Y63" s="34">
+      <c r="Y63" s="35">
         <v>0.91</v>
       </c>
-      <c r="Z63" s="34">
+      <c r="Z63" s="35">
         <v>0.89</v>
       </c>
-      <c r="AA63" s="34">
+      <c r="AA63" s="35">
         <v>0.92</v>
       </c>
-      <c r="AB63" s="34">
+      <c r="AB63" s="35">
         <v>0.93</v>
       </c>
-      <c r="AC63" s="31"/>
-      <c r="AD63" s="31"/>
-      <c r="AE63" s="31"/>
-      <c r="AF63" s="31"/>
+      <c r="AC63" s="32"/>
+      <c r="AD63" s="32"/>
+      <c r="AE63" s="32"/>
+      <c r="AF63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
-      <c r="AA64" s="29"/>
-      <c r="AB64" s="29"/>
-      <c r="AC64" s="29"/>
-      <c r="AD64" s="29"/>
-      <c r="AE64" s="29"/>
-      <c r="AF64" s="29"/>
+      <c r="A64" s="29" t="s">
+        <v>429</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
+      <c r="AE64" s="30"/>
+      <c r="AF64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="B65" s="34">
+      <c r="A65" s="31" t="s">
+        <v>430</v>
+      </c>
+      <c r="B65" s="35">
         <v>25.41</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="35">
         <v>26.57</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="35">
         <v>25.1</v>
       </c>
-      <c r="E65" s="34">
+      <c r="E65" s="35">
         <v>29.21</v>
       </c>
-      <c r="F65" s="34">
+      <c r="F65" s="35">
         <v>64.3</v>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="35">
         <v>66.22</v>
       </c>
-      <c r="H65" s="34">
+      <c r="H65" s="35">
         <v>66.09</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="33">
         <v>104.31</v>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="35">
         <v>29.94</v>
       </c>
-      <c r="K65" s="34">
+      <c r="K65" s="35">
         <v>13.16</v>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="35">
         <v>18.02</v>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="35">
         <v>13.38</v>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="35">
         <v>21.97</v>
       </c>
-      <c r="O65" s="34">
+      <c r="O65" s="35">
         <v>11.23</v>
       </c>
-      <c r="P65" s="34">
+      <c r="P65" s="35">
         <v>4.44</v>
       </c>
-      <c r="Q65" s="34">
+      <c r="Q65" s="35">
         <v>7.59</v>
       </c>
-      <c r="R65" s="34">
+      <c r="R65" s="35">
         <v>10.58</v>
       </c>
-      <c r="S65" s="34">
+      <c r="S65" s="35">
         <v>16.52</v>
       </c>
-      <c r="T65" s="34">
+      <c r="T65" s="35">
         <v>12.81</v>
       </c>
-      <c r="U65" s="31"/>
-      <c r="V65" s="34">
+      <c r="U65" s="32"/>
+      <c r="V65" s="35">
         <v>34.43</v>
       </c>
-      <c r="W65" s="37">
+      <c r="W65" s="38">
         <v>-0.88</v>
       </c>
-      <c r="X65" s="34">
+      <c r="X65" s="35">
         <v>1.68</v>
       </c>
-      <c r="Y65" s="34">
+      <c r="Y65" s="35">
         <v>1.52</v>
       </c>
-      <c r="Z65" s="34">
+      <c r="Z65" s="35">
         <v>1.38</v>
       </c>
-      <c r="AA65" s="34">
+      <c r="AA65" s="35">
         <v>1.58</v>
       </c>
-      <c r="AB65" s="34">
+      <c r="AB65" s="35">
         <v>1.56</v>
       </c>
-      <c r="AC65" s="34">
+      <c r="AC65" s="35">
         <v>1.65</v>
       </c>
-      <c r="AD65" s="34">
+      <c r="AD65" s="35">
         <v>1.27</v>
       </c>
-      <c r="AE65" s="31"/>
-      <c r="AF65" s="34">
+      <c r="AE65" s="32"/>
+      <c r="AF65" s="35">
         <v>1.6</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>429</v>
-      </c>
-      <c r="B66" s="34">
+      <c r="A66" s="31" t="s">
+        <v>431</v>
+      </c>
+      <c r="B66" s="35">
         <v>30.03</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="35">
         <v>35.92</v>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="35">
         <v>43.11</v>
       </c>
-      <c r="E66" s="34">
+      <c r="E66" s="35">
         <v>53.99</v>
       </c>
-      <c r="F66" s="34">
+      <c r="F66" s="35">
         <v>62.0</v>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="35">
         <v>42.2</v>
       </c>
-      <c r="H66" s="34">
+      <c r="H66" s="35">
         <v>30.25</v>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="35">
         <v>21.27</v>
       </c>
-      <c r="J66" s="34">
+      <c r="J66" s="35">
         <v>17.44</v>
       </c>
-      <c r="K66" s="34">
+      <c r="K66" s="35">
         <v>15.04</v>
       </c>
-      <c r="L66" s="34">
+      <c r="L66" s="35">
         <v>12.96</v>
       </c>
-      <c r="M66" s="34">
+      <c r="M66" s="35">
         <v>10.71</v>
       </c>
-      <c r="N66" s="34">
+      <c r="N66" s="35">
         <v>9.99</v>
       </c>
-      <c r="O66" s="34">
+      <c r="O66" s="35">
         <v>9.22</v>
       </c>
-      <c r="P66" s="34">
+      <c r="P66" s="35">
         <v>9.58</v>
       </c>
-      <c r="Q66" s="31"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="31"/>
-      <c r="T66" s="31"/>
-      <c r="U66" s="31"/>
-      <c r="V66" s="34">
+      <c r="Q66" s="32"/>
+      <c r="R66" s="32"/>
+      <c r="S66" s="32"/>
+      <c r="T66" s="32"/>
+      <c r="U66" s="32"/>
+      <c r="V66" s="35">
         <v>2.13</v>
       </c>
-      <c r="W66" s="34">
+      <c r="W66" s="35">
         <v>1.48</v>
       </c>
-      <c r="X66" s="34">
+      <c r="X66" s="35">
         <v>1.54</v>
       </c>
-      <c r="Y66" s="34">
+      <c r="Y66" s="35">
         <v>1.53</v>
       </c>
-      <c r="Z66" s="34">
+      <c r="Z66" s="35">
         <v>1.49</v>
       </c>
-      <c r="AA66" s="34">
+      <c r="AA66" s="35">
         <v>2.02</v>
       </c>
-      <c r="AB66" s="34">
+      <c r="AB66" s="35">
         <v>2.11</v>
       </c>
-      <c r="AC66" s="31"/>
-      <c r="AD66" s="31"/>
-      <c r="AE66" s="31"/>
-      <c r="AF66" s="31"/>
+      <c r="AC66" s="32"/>
+      <c r="AD66" s="32"/>
+      <c r="AE66" s="32"/>
+      <c r="AF66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>430</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
-      <c r="AA67" s="29"/>
-      <c r="AB67" s="29"/>
-      <c r="AC67" s="29"/>
-      <c r="AD67" s="29"/>
-      <c r="AE67" s="29"/>
-      <c r="AF67" s="29"/>
+      <c r="A67" s="29" t="s">
+        <v>432</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
+      <c r="AD67" s="30"/>
+      <c r="AE67" s="30"/>
+      <c r="AF67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="31" t="s">
+        <v>433</v>
+      </c>
+      <c r="B68" s="35">
         <v>27.58</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <v>29.72</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <v>34.24</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="35">
         <v>52.59</v>
       </c>
-      <c r="F68" s="34">
+      <c r="F68" s="35">
         <v>75.71</v>
       </c>
-      <c r="G68" s="34">
+      <c r="G68" s="35">
         <v>86.69</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="33">
         <v>131.19</v>
       </c>
-      <c r="I68" s="31"/>
-      <c r="J68" s="31"/>
-      <c r="K68" s="34">
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="35">
         <v>20.86</v>
       </c>
-      <c r="L68" s="34">
+      <c r="L68" s="35">
         <v>44.5</v>
       </c>
-      <c r="M68" s="34">
+      <c r="M68" s="35">
         <v>18.93</v>
       </c>
-      <c r="N68" s="34">
+      <c r="N68" s="35">
         <v>38.83</v>
       </c>
-      <c r="O68" s="34">
+      <c r="O68" s="35">
         <v>13.97</v>
       </c>
-      <c r="P68" s="34">
+      <c r="P68" s="35">
         <v>5.18</v>
       </c>
-      <c r="Q68" s="34">
+      <c r="Q68" s="35">
         <v>10.03</v>
       </c>
-      <c r="R68" s="34">
+      <c r="R68" s="35">
         <v>13.1</v>
       </c>
-      <c r="S68" s="34">
+      <c r="S68" s="35">
         <v>23.16</v>
       </c>
-      <c r="T68" s="34">
+      <c r="T68" s="35">
         <v>12.57</v>
       </c>
-      <c r="U68" s="31"/>
-      <c r="V68" s="32">
+      <c r="U68" s="32"/>
+      <c r="V68" s="33">
         <v>100.98</v>
       </c>
-      <c r="W68" s="37">
+      <c r="W68" s="38">
         <v>-1.43</v>
       </c>
-      <c r="X68" s="34">
+      <c r="X68" s="35">
         <v>13.63</v>
       </c>
-      <c r="Y68" s="34">
+      <c r="Y68" s="35">
         <v>14.52</v>
       </c>
-      <c r="Z68" s="34">
+      <c r="Z68" s="35">
         <v>6.54</v>
       </c>
-      <c r="AA68" s="34">
+      <c r="AA68" s="35">
         <v>16.67</v>
       </c>
-      <c r="AB68" s="34">
+      <c r="AB68" s="35">
         <v>25.3</v>
       </c>
-      <c r="AC68" s="34">
+      <c r="AC68" s="35">
         <v>10.84</v>
       </c>
-      <c r="AD68" s="34">
+      <c r="AD68" s="35">
         <v>8.3</v>
       </c>
-      <c r="AE68" s="34">
+      <c r="AE68" s="35">
         <v>15.04</v>
       </c>
-      <c r="AF68" s="32">
+      <c r="AF68" s="33">
         <v>314.98</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="B69" s="34">
+      <c r="A69" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="B69" s="35">
         <v>36.3</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="35">
         <v>46.42</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="35">
         <v>62.28</v>
       </c>
-      <c r="E69" s="34">
+      <c r="E69" s="35">
         <v>90.7</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="33">
         <v>230.39</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <v>195.37</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="33">
         <v>216.82</v>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="35">
         <v>94.71</v>
       </c>
-      <c r="J69" s="34">
+      <c r="J69" s="35">
         <v>53.82</v>
       </c>
-      <c r="K69" s="34">
+      <c r="K69" s="35">
         <v>24.43</v>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="35">
         <v>19.26</v>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="35">
         <v>14.22</v>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="35">
         <v>12.89</v>
       </c>
-      <c r="O69" s="34">
+      <c r="O69" s="35">
         <v>11.57</v>
       </c>
-      <c r="P69" s="34">
+      <c r="P69" s="35">
         <v>11.42</v>
       </c>
-      <c r="Q69" s="31"/>
-      <c r="R69" s="31"/>
-      <c r="S69" s="31"/>
-      <c r="T69" s="31"/>
-      <c r="U69" s="31"/>
-      <c r="V69" s="34">
+      <c r="Q69" s="32"/>
+      <c r="R69" s="32"/>
+      <c r="S69" s="32"/>
+      <c r="T69" s="32"/>
+      <c r="U69" s="32"/>
+      <c r="V69" s="35">
         <v>12.85</v>
       </c>
-      <c r="W69" s="34">
+      <c r="W69" s="35">
         <v>10.11</v>
       </c>
-      <c r="X69" s="34">
+      <c r="X69" s="35">
         <v>12.95</v>
       </c>
-      <c r="Y69" s="34">
+      <c r="Y69" s="35">
         <v>12.35</v>
       </c>
-      <c r="Z69" s="34">
+      <c r="Z69" s="35">
         <v>11.21</v>
       </c>
-      <c r="AA69" s="34">
+      <c r="AA69" s="35">
         <v>13.85</v>
       </c>
-      <c r="AB69" s="34">
+      <c r="AB69" s="35">
         <v>15.1</v>
       </c>
-      <c r="AC69" s="31"/>
-      <c r="AD69" s="31"/>
-      <c r="AE69" s="31"/>
-      <c r="AF69" s="31"/>
+      <c r="AC69" s="32"/>
+      <c r="AD69" s="32"/>
+      <c r="AE69" s="32"/>
+      <c r="AF69" s="32"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>433</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Y70" s="29"/>
-      <c r="Z70" s="29"/>
-      <c r="AA70" s="29"/>
-      <c r="AB70" s="29"/>
-      <c r="AC70" s="29"/>
-      <c r="AD70" s="29"/>
-      <c r="AE70" s="29"/>
-      <c r="AF70" s="29"/>
+      <c r="A70" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+      <c r="AB70" s="30"/>
+      <c r="AC70" s="30"/>
+      <c r="AD70" s="30"/>
+      <c r="AE70" s="30"/>
+      <c r="AF70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>434</v>
-      </c>
-      <c r="B71" s="34">
+      <c r="A71" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="B71" s="35">
         <v>34.4</v>
       </c>
-      <c r="C71" s="31"/>
-      <c r="D71" s="34">
+      <c r="C71" s="32"/>
+      <c r="D71" s="35">
         <v>79.31</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="33">
         <v>347.26</v>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="33">
         <v>172.83</v>
       </c>
-      <c r="G71" s="32">
+      <c r="G71" s="33">
         <v>330.28</v>
       </c>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="34">
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="35">
         <v>46.94</v>
       </c>
-      <c r="L71" s="31"/>
-      <c r="M71" s="34">
+      <c r="L71" s="32"/>
+      <c r="M71" s="35">
         <v>51.35</v>
       </c>
-      <c r="N71" s="31"/>
-      <c r="O71" s="32">
+      <c r="N71" s="32"/>
+      <c r="O71" s="33">
         <v>1145.59</v>
       </c>
-      <c r="P71" s="34">
+      <c r="P71" s="35">
         <v>8.02</v>
       </c>
-      <c r="Q71" s="34">
+      <c r="Q71" s="35">
         <v>24.54</v>
       </c>
-      <c r="R71" s="34">
+      <c r="R71" s="35">
         <v>79.19</v>
       </c>
-      <c r="S71" s="31"/>
-      <c r="T71" s="34">
+      <c r="S71" s="32"/>
+      <c r="T71" s="35">
         <v>23.81</v>
       </c>
-      <c r="U71" s="31"/>
-      <c r="V71" s="31"/>
-      <c r="W71" s="37">
+      <c r="U71" s="32"/>
+      <c r="V71" s="32"/>
+      <c r="W71" s="38">
         <v>-2.82</v>
       </c>
-      <c r="X71" s="31"/>
-      <c r="Y71" s="31"/>
-      <c r="Z71" s="34">
+      <c r="X71" s="32"/>
+      <c r="Y71" s="32"/>
+      <c r="Z71" s="35">
         <v>14.08</v>
       </c>
-      <c r="AA71" s="31"/>
-      <c r="AB71" s="31"/>
-      <c r="AC71" s="31"/>
-      <c r="AD71" s="31"/>
-      <c r="AE71" s="31"/>
-      <c r="AF71" s="31"/>
+      <c r="AA71" s="32"/>
+      <c r="AB71" s="32"/>
+      <c r="AC71" s="32"/>
+      <c r="AD71" s="32"/>
+      <c r="AE71" s="32"/>
+      <c r="AF71" s="32"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="B72" s="34">
+      <c r="A72" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B72" s="35">
         <v>86.49</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="33">
         <v>261.08</v>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="33">
         <v>205.93</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="33">
         <v>2841.9</v>
       </c>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
-      <c r="K72" s="32">
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="33">
         <v>178.4</v>
       </c>
-      <c r="L72" s="34">
+      <c r="L72" s="35">
         <v>92.53</v>
       </c>
-      <c r="M72" s="34">
+      <c r="M72" s="35">
         <v>49.86</v>
       </c>
-      <c r="N72" s="34">
+      <c r="N72" s="35">
         <v>53.16</v>
       </c>
-      <c r="O72" s="34">
+      <c r="O72" s="35">
         <v>66.38</v>
       </c>
-      <c r="P72" s="34">
+      <c r="P72" s="35">
         <v>40.07</v>
       </c>
-      <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
-      <c r="S72" s="31"/>
-      <c r="T72" s="31"/>
-      <c r="U72" s="31"/>
-      <c r="V72" s="34">
+      <c r="Q72" s="32"/>
+      <c r="R72" s="32"/>
+      <c r="S72" s="32"/>
+      <c r="T72" s="32"/>
+      <c r="U72" s="32"/>
+      <c r="V72" s="35">
         <v>76.47</v>
       </c>
-      <c r="W72" s="32">
+      <c r="W72" s="33">
         <v>106.63</v>
       </c>
-      <c r="X72" s="31"/>
-      <c r="Y72" s="31"/>
-      <c r="Z72" s="31"/>
-      <c r="AA72" s="31"/>
-      <c r="AB72" s="31"/>
-      <c r="AC72" s="31"/>
-      <c r="AD72" s="31"/>
-      <c r="AE72" s="31"/>
-      <c r="AF72" s="31"/>
+      <c r="X72" s="32"/>
+      <c r="Y72" s="32"/>
+      <c r="Z72" s="32"/>
+      <c r="AA72" s="32"/>
+      <c r="AB72" s="32"/>
+      <c r="AC72" s="32"/>
+      <c r="AD72" s="32"/>
+      <c r="AE72" s="32"/>
+      <c r="AF72" s="32"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/cox_xlsx/ALKb.CO.xlsx
+++ b/data/cox_xlsx/ALKb.CO.xlsx
@@ -15628,8 +15628,8 @@
       <c r="W106" s="20"/>
     </row>
     <row r="107" ht="15.0" customHeight="1">
-      <c r="A107" s="16" t="s">
-        <v>260</v>
+      <c r="A107" s="28" t="s">
+        <v>276</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
